--- a/result/correlation_analysis_organelle_volume.xlsx
+++ b/result/correlation_analysis_organelle_volume.xlsx
@@ -1132,79 +1132,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8536824677181396</v>
+        <v>0.85368246771814</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5131101431178604</v>
+        <v>0.5131101431178605</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9374469410714795</v>
+        <v>0.9374469410714803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7617400612550869</v>
+        <v>0.9726496295229399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8287448222077043</v>
+        <v>0.8287448222077048</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9037334889377141</v>
+        <v>0.9037334889377143</v>
       </c>
       <c r="H2" t="n">
         <v>0.8375691575814</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7718534649220912</v>
+        <v>0.7718534649220916</v>
       </c>
       <c r="J2" t="n">
-        <v>0.858518632500828</v>
+        <v>0.9445865653336004</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7553480843394534</v>
+        <v>0.7553480843394538</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9441733438565012</v>
+        <v>0.944173343856501</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7820205279760151</v>
+        <v>0.782020527976015</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5945495556458552</v>
+        <v>0.5945495556458555</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7851807981814435</v>
+        <v>0.7851807981814436</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9532108851977517</v>
+        <v>0.9532108851977519</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7842303185720834</v>
+        <v>0.7842303185720836</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9223125182033169</v>
+        <v>0.9223125182033171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9622072169269025</v>
+        <v>0.9622072169269024</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9622041626958172</v>
+        <v>0.9622041626958173</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9481028601718001</v>
+        <v>0.9481028601718003</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9504630398017294</v>
+        <v>0.9504630398017293</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7697271591894219</v>
+        <v>0.7697271591894217</v>
       </c>
       <c r="X2" t="n">
         <v>0.9614621285315856</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9441926064957302</v>
+        <v>0.94419260649573</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9353707475329608</v>
+        <v>0.9353707475329609</v>
       </c>
       <c r="AA2" t="n">
         <v>0.9492172787434554</v>
@@ -1213,22 +1213,22 @@
         <v>0.923314576957518</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.820685412567616</v>
+        <v>0.8206854125676167</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6486872831995052</v>
+        <v>0.6486872831995064</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.8113794701137449</v>
+        <v>0.811379470113746</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.9147557914451889</v>
+        <v>0.9147557914451888</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.8023772004109473</v>
+        <v>0.8023772004109472</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.9405536687350418</v>
+        <v>0.940553668735042</v>
       </c>
       <c r="AI2" t="n">
         <v>0.9328973050707131</v>
@@ -1240,79 +1240,79 @@
         <v>0.8956940984257344</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8764537901853984</v>
+        <v>0.876453790185398</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8375572669352573</v>
+        <v>0.8375572669352571</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.929384700464807</v>
+        <v>0.9293847004648073</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8873047364085255</v>
+        <v>0.8873047364085249</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.8251798082824325</v>
+        <v>0.8251798082824326</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9610935764216428</v>
+        <v>0.9610935764216429</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.951514216926394</v>
+        <v>0.9515142169263942</v>
       </c>
       <c r="AS2" t="n">
         <v>0.9278443424792542</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.718336372346659</v>
+        <v>0.7183363723466608</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.7068848640253093</v>
+        <v>0.7068848640253108</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.865817100497795</v>
+        <v>0.8658171004977948</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9541235614057541</v>
+        <v>0.9541235614057536</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.9546953893935316</v>
+        <v>0.9546953893935313</v>
       </c>
       <c r="AY2" t="n">
         <v>0.9470353794461741</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.9449406092159279</v>
+        <v>0.944940609215928</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.7206325958354167</v>
+        <v>0.7206325958354194</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.8420383976484247</v>
+        <v>0.8420383976484248</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.912978761352347</v>
+        <v>0.9129787613523468</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.9606545608245183</v>
+        <v>0.9606545608245182</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.8940700159986125</v>
+        <v>0.8940700159986124</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.9074099535529188</v>
+        <v>0.9074099535529183</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.8971828709498089</v>
+        <v>0.8971828709498086</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.9514321535648687</v>
+        <v>0.9514321535648688</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.8615843517743857</v>
+        <v>0.8615843517743856</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.07719331614303296</v>
+        <v>-0.07719331614303304</v>
       </c>
       <c r="BK2" t="n">
         <v>-0.6775805810557427</v>
@@ -1321,67 +1321,67 @@
         <v>0.9650619546453527</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6277842197364658</v>
+        <v>0.6277842197364657</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.9399315713723061</v>
+        <v>0.9399315713723062</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1811083287476982</v>
+        <v>0.1811083287476974</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.9383123400842317</v>
+        <v>0.9383123400842325</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.9410201212741612</v>
+        <v>0.9410201212741613</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.7239451343560172</v>
+        <v>-0.7239451343560174</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.7612221765773586</v>
+        <v>0.7612221765773585</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.9345815432621424</v>
+        <v>0.9345815432621423</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.914163037218914</v>
+        <v>0.9141630372189142</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9024525633278642</v>
+        <v>0.9024525633278641</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.6137411344564587</v>
+        <v>0.6137411344564596</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.9230587181222532</v>
+        <v>0.9230587181222529</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.9701044069016009</v>
+        <v>0.9701044069016006</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.4277764512978062</v>
+        <v>-0.4277764512978058</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.8491842761844171</v>
+        <v>0.8491842761844172</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.9339083255789674</v>
+        <v>0.9339083255789671</v>
       </c>
       <c r="CC2" t="n">
         <v>0.6791546680505145</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.9470294843580709</v>
+        <v>0.947029484358071</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.9777296691544751</v>
+        <v>0.977729669154475</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.9649406816063183</v>
+        <v>0.9649406816063184</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.5508779651191319</v>
+        <v>0.5508779651191316</v>
       </c>
       <c r="CH2" t="n">
         <v>0.9379877629996184</v>
@@ -1390,16 +1390,16 @@
         <v>0.9126894535561141</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.361078051985115</v>
+        <v>0.3610780519851152</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.9211038779445474</v>
+        <v>0.9211038779445465</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.8836392469053862</v>
+        <v>0.8836392469053864</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.8618159860063441</v>
+        <v>0.8618159860063432</v>
       </c>
       <c r="CN2" t="n">
         <v>0.9495502051729473</v>
@@ -1408,79 +1408,79 @@
         <v>0.504666874711436</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.5352788227820668</v>
+        <v>0.535278822782067</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.03052013445638212</v>
+        <v>0.03052013445638329</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.9684629682159792</v>
+        <v>0.9684629682159793</v>
       </c>
       <c r="CS2" t="n">
         <v>0.9736474749885753</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.9793869056191745</v>
+        <v>0.9793869056191743</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.9740595064584412</v>
+        <v>0.9740595064584413</v>
       </c>
       <c r="CV2" t="n">
         <v>0.9133460100735045</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.8919114839532916</v>
+        <v>0.8919114839532912</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.8652364849812836</v>
+        <v>0.8652364849812837</v>
       </c>
       <c r="CY2" t="n">
         <v>0.9389841765307317</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.9070493820860634</v>
+        <v>0.9070493820860633</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.9172041489353603</v>
+        <v>0.9172041489353604</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.8513913618993828</v>
+        <v>0.8513913618993824</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.8569874369512657</v>
+        <v>0.8569874369512656</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.9271857020561733</v>
+        <v>0.9271857020561736</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.9370649215319747</v>
+        <v>0.9370649215319684</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.8782531251217554</v>
+        <v>0.8782531251217555</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.8710466414062077</v>
+        <v>0.8710466414062078</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.8871862763279056</v>
+        <v>0.887186276327905</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.9055280851151379</v>
+        <v>0.905528085115138</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.9155969367302179</v>
+        <v>0.9155969367302172</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.9691604199749095</v>
+        <v>0.9691604199749096</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.859022510238021</v>
+        <v>0.8590225102380219</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.9309187100020682</v>
+        <v>0.9309187100020679</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9643759082503455</v>
+        <v>0.9643759082503456</v>
       </c>
       <c r="DO2" t="n">
         <v>0.9555567933447545</v>
@@ -1489,64 +1489,64 @@
         <v>0.9485359979004313</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.2137954717790646</v>
+        <v>-0.2137954717790667</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.3385468543219513</v>
+        <v>0.3385468543219525</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.9208717005056468</v>
+        <v>0.9208717005056469</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.8962988638804011</v>
+        <v>0.8962988638804013</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.8761825479223992</v>
+        <v>0.8761825479223991</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.8718334519684648</v>
+        <v>0.8718334519684656</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.974010616122964</v>
+        <v>0.9740106161229639</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.8158489558477143</v>
+        <v>0.8158489558477146</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.932641308965569</v>
+        <v>0.9326413089655688</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.9218352179587033</v>
+        <v>0.9218352179587034</v>
       </c>
       <c r="EA2" t="n">
         <v>0.9730506879598229</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.960492982650575</v>
+        <v>0.9604929826505749</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.9723304617136249</v>
+        <v>0.972330461713625</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.05298272316273109</v>
+        <v>0.05298272316273053</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.888666819302858</v>
+        <v>0.8886668193028582</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.04848009990229499</v>
+        <v>0.04848009990228052</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.8124943594269641</v>
+        <v>0.8124943594269636</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.7841594767838009</v>
+        <v>0.7841594767837975</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.8288387845321248</v>
+        <v>0.828838784532129</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.7957684712255624</v>
+        <v>0.7957684712255635</v>
       </c>
     </row>
     <row r="3">
@@ -1556,211 +1556,211 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9356805823307934</v>
+        <v>0.9356805823307939</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6162290711774298</v>
+        <v>0.61622907117743</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9733376816583422</v>
+        <v>0.9733376816583432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8876505586933925</v>
+        <v>0.9509821094657315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9291261407019299</v>
+        <v>0.9291261407019303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.973479803826691</v>
+        <v>0.9734798038266913</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9319131161068499</v>
+        <v>0.93191311610685</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8981345512365808</v>
+        <v>0.8981345512365811</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9478103247352297</v>
+        <v>0.9052678461496757</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8734158805301404</v>
+        <v>0.8734158805301405</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9539128917762396</v>
+        <v>0.9539128917762395</v>
       </c>
       <c r="M3" t="n">
         <v>0.6602246673673399</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6606740273822397</v>
+        <v>0.66067402738224</v>
       </c>
       <c r="O3" t="n">
         <v>0.7695644862055607</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9421909492351567</v>
+        <v>0.9421909492351571</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.736974022251444</v>
+        <v>0.7369740222514443</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9617832020832459</v>
+        <v>0.961783202083246</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9695713949783507</v>
+        <v>0.9695713949783504</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9728658029828858</v>
+        <v>0.9728658029828857</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9520616540320249</v>
+        <v>0.9520616540320251</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9531535231177937</v>
+        <v>0.9531535231177936</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8542362729752498</v>
+        <v>0.8542362729752496</v>
       </c>
       <c r="X3" t="n">
         <v>0.95807905099373</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9561434693987049</v>
+        <v>0.9561434693987046</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9284021873010821</v>
+        <v>0.9284021873010824</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.993285524901353</v>
+        <v>0.9932855249013531</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9447806504460481</v>
+        <v>0.9447806504460483</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8848079800898012</v>
+        <v>0.8848079800898017</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.6923617609982168</v>
+        <v>0.6923617609982178</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.8548623451748479</v>
+        <v>0.854862345174849</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.9783625896232243</v>
+        <v>0.9783625896232244</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.8519398826067319</v>
+        <v>0.8519398826067318</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9722900849981997</v>
+        <v>0.9722900849981998</v>
       </c>
       <c r="AI3" t="n">
         <v>0.9387925465205863</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9629458882962273</v>
+        <v>0.9629458882962274</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8548364466972351</v>
+        <v>0.8548364466972352</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.93208826047145</v>
+        <v>0.9320882604714498</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8944916199056003</v>
+        <v>0.8944916199056</v>
       </c>
       <c r="AN3" t="n">
         <v>0.9637526213322258</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8919544228728128</v>
+        <v>0.891954422872812</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.8277804715341174</v>
+        <v>0.827780471534117</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.9598127520604391</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.970398164493196</v>
+        <v>0.9703981644931959</v>
       </c>
       <c r="AS3" t="n">
         <v>0.96136457874583</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.6691764591813245</v>
+        <v>0.6691764591813261</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.7748553186467175</v>
+        <v>0.7748553186467191</v>
       </c>
       <c r="AV3" t="n">
         <v>0.9333818711318016</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9150482900640242</v>
+        <v>0.9150482900640238</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.9830994987455429</v>
+        <v>0.9830994987455426</v>
       </c>
       <c r="AY3" t="n">
         <v>0.9948573056118112</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.8995690295837477</v>
+        <v>0.899569029583748</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.7935486589364751</v>
+        <v>0.793548658936478</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.9434809934071838</v>
+        <v>0.9434809934071837</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.9345489359297812</v>
+        <v>0.9345489359297809</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.9059924967732562</v>
+        <v>0.9059924967732559</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.9489667556224455</v>
+        <v>0.9489667556224454</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.921131312292266</v>
+        <v>0.9211313122922657</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.8825682575644396</v>
+        <v>0.8825682575644394</v>
       </c>
       <c r="BH3" t="n">
         <v>0.918993057272004</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.9270316752305099</v>
+        <v>0.92703167523051</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.04945383595264755</v>
+        <v>-0.04945383595264757</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.522900259853975</v>
+        <v>-0.5229002598539751</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9738399769711384</v>
+        <v>0.9738399769711382</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.7399594106862331</v>
+        <v>0.7399594106862329</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.9397402421200242</v>
+        <v>0.939740242120024</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.3262726053601793</v>
+        <v>0.3262726053601789</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.9273061089703694</v>
+        <v>0.9273061089703696</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.9726900927866277</v>
+        <v>0.9726900927866275</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.5851801732592258</v>
+        <v>-0.5851801732592259</v>
       </c>
       <c r="BS3" t="n">
         <v>0.8018771239743597</v>
@@ -1775,25 +1775,25 @@
         <v>0.9190955506535262</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.6658706244237427</v>
+        <v>0.6658706244237432</v>
       </c>
       <c r="BX3" t="n">
         <v>0.9532599289308685</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.973817826711187</v>
+        <v>0.9738178267111873</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.4558146218228255</v>
+        <v>-0.4558146218228253</v>
       </c>
       <c r="CA3" t="n">
         <v>0.867085720873886</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.9776688710923334</v>
+        <v>0.9776688710923332</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.7716252055735034</v>
+        <v>0.7716252055735037</v>
       </c>
       <c r="CD3" t="n">
         <v>0.8793487134050936</v>
@@ -1802,109 +1802,109 @@
         <v>0.9466407446030549</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.9635692673404814</v>
+        <v>0.9635692673404815</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.3871898534917021</v>
+        <v>0.3871898534917018</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.9455798012529009</v>
+        <v>0.945579801252901</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.9589693618781837</v>
+        <v>0.9589693618781835</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.2314627490754833</v>
+        <v>0.2314627490754835</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.9302848099229855</v>
+        <v>0.930284809922984</v>
       </c>
       <c r="CL3" t="n">
         <v>0.9381412466605339</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.8715995086855917</v>
+        <v>0.8715995086855903</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.9623337489149524</v>
+        <v>0.9623337489149523</v>
       </c>
       <c r="CO3" t="n">
         <v>0.6276014683379326</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.5917449987691659</v>
+        <v>0.591744998769166</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001733612948242168</v>
+        <v>0.001733612948243389</v>
       </c>
       <c r="CR3" t="n">
         <v>0.9533436755853298</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.9730518739515537</v>
+        <v>0.9730518739515538</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.9526763642449957</v>
+        <v>0.9526763642449956</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.9436815341500078</v>
+        <v>0.9436815341500079</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.9310332137636602</v>
+        <v>0.9310332137636603</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.9173585001519251</v>
+        <v>0.9173585001519249</v>
       </c>
       <c r="CX3" t="n">
         <v>0.9217574085827538</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.9450608766852443</v>
+        <v>0.945060876685244</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.8982346313738019</v>
+        <v>0.8982346313738021</v>
       </c>
       <c r="DA3" t="n">
         <v>0.9204767306013217</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.8534598863699029</v>
+        <v>0.8534598863699023</v>
       </c>
       <c r="DC3" t="n">
         <v>0.926297428890495</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.9280922316597212</v>
+        <v>0.9280922316597213</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.9249778698892136</v>
+        <v>0.9249778698892034</v>
       </c>
       <c r="DF3" t="n">
         <v>0.9140076465575226</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.9217146455498872</v>
+        <v>0.9217146455498876</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.940262013223035</v>
+        <v>0.9402620132230347</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.9405136694585635</v>
+        <v>0.9405136694585634</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.9167175571018104</v>
+        <v>0.9167175571018106</v>
       </c>
       <c r="DK3" t="n">
         <v>0.9807803829681262</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.8866519503705979</v>
+        <v>0.886651950370599</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.9669365902494074</v>
+        <v>0.9669365902494071</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.97224404618349</v>
+        <v>0.9722440461834899</v>
       </c>
       <c r="DO3" t="n">
         <v>0.8913110940946556</v>
@@ -1913,10 +1913,10 @@
         <v>0.9934945900985568</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.08289181578905147</v>
+        <v>-0.08289181578905319</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2788737671873127</v>
+        <v>0.2788737671873139</v>
       </c>
       <c r="DS3" t="n">
         <v>0.9702838515643875</v>
@@ -1925,16 +1925,16 @@
         <v>0.8648816615748296</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.8797344650642799</v>
+        <v>0.8797344650642798</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.8979067753027432</v>
+        <v>0.897906775302744</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.982022113629764</v>
+        <v>0.9820221136297641</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.8481989517261403</v>
+        <v>0.8481989517261405</v>
       </c>
       <c r="DY3" t="n">
         <v>0.9711519691488195</v>
@@ -1946,31 +1946,31 @@
         <v>0.9679292239654989</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.9642102833621491</v>
+        <v>0.9642102833621492</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.9933499554115028</v>
+        <v>0.9933499554115029</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0877890837636438</v>
+        <v>0.08778908376364188</v>
       </c>
       <c r="EE3" t="n">
         <v>0.9434596923666334</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.08264008607009875</v>
+        <v>-0.08264008607011254</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.663368159718241</v>
+        <v>0.6633681597182403</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.7652513591002681</v>
+        <v>0.765251359100263</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.8150138363084074</v>
+        <v>0.8150138363084114</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.8296280622691407</v>
+        <v>0.8296280622691411</v>
       </c>
     </row>
     <row r="4">
@@ -1980,244 +1980,244 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9332968088011391</v>
+        <v>0.9332968088011394</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6076066854901532</v>
+        <v>0.6076066854901533</v>
       </c>
       <c r="D4" t="n">
-        <v>0.97270691053115</v>
+        <v>0.9727069105311508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.886212196078968</v>
+        <v>0.9497358239326603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9272213412003578</v>
+        <v>0.9272213412003583</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9718398680106433</v>
+        <v>0.9718398680106435</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9310226521605464</v>
+        <v>0.9310226521605465</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8972155080666441</v>
+        <v>0.8972155080666443</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9460810346434863</v>
+        <v>0.9063714047005833</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8726926361090379</v>
+        <v>0.8726926361090381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9521563234249355</v>
+        <v>0.9521563234249353</v>
       </c>
       <c r="M4" t="n">
         <v>0.6598786610667637</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6559934284741471</v>
+        <v>0.6559934284741475</v>
       </c>
       <c r="O4" t="n">
         <v>0.7699081025259391</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9406788131156854</v>
+        <v>0.9406788131156859</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7366380255145321</v>
+        <v>0.7366380255145323</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9607032087834719</v>
+        <v>0.9607032087834722</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9690696375938108</v>
+        <v>0.9690696375938106</v>
       </c>
       <c r="T4" t="n">
-        <v>0.971261535043862</v>
+        <v>0.9712615350438619</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9519068366802281</v>
+        <v>0.9519068366802284</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9515463510330104</v>
+        <v>0.9515463510330107</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8543675646054956</v>
+        <v>0.8543675646054953</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9575802168349642</v>
+        <v>0.957580216834964</v>
       </c>
       <c r="Y4" t="n">
         <v>0.9544048982277722</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9278560971188958</v>
+        <v>0.9278560971188961</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9925288272657689</v>
+        <v>0.992528827265769</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9420609943643687</v>
+        <v>0.9420609943643691</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8800490458294112</v>
+        <v>0.8800490458294116</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6866757587818276</v>
+        <v>0.6866757587818288</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.8497588013730772</v>
+        <v>0.8497588013730784</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.9776385858658873</v>
+        <v>0.9776385858658874</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.8498646560056602</v>
+        <v>0.8498646560056599</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.9711143163386067</v>
+        <v>0.9711143163386068</v>
       </c>
       <c r="AI4" t="n">
         <v>0.937110791177604</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9608561996133691</v>
+        <v>0.9608561996133693</v>
       </c>
       <c r="AK4" t="n">
         <v>0.8538765041270722</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9284369927822262</v>
+        <v>0.928436992782226</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8901038534176626</v>
+        <v>0.8901038534176624</v>
       </c>
       <c r="AN4" t="n">
         <v>0.9629091518586739</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8903715495847603</v>
+        <v>0.8903715495847597</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.8263264223258011</v>
+        <v>0.826326422325801</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9590411289742526</v>
+        <v>0.9590411289742529</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9684777828396735</v>
+        <v>0.9684777828396736</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.9600756216611436</v>
+        <v>0.9600756216611438</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.667050684994231</v>
+        <v>0.6670506849942327</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.7683192206780582</v>
+        <v>0.7683192206780598</v>
       </c>
       <c r="AV4" t="n">
         <v>0.9307068246640668</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.9131921943327804</v>
+        <v>0.9131921943327801</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.981575499741862</v>
+        <v>0.9815754997418618</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.994211563357233</v>
+        <v>0.9942115633572332</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.8981306425298132</v>
+        <v>0.8981306425298137</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.7861744486161146</v>
+        <v>0.7861744486161176</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.9410884955998031</v>
+        <v>0.9410884955998033</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.9351301290306764</v>
+        <v>0.9351301290306762</v>
       </c>
       <c r="BD4" t="n">
         <v>0.9056695800937841</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.9481160914818674</v>
+        <v>0.9481160914818673</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.9188208397456269</v>
+        <v>0.9188208397456266</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.882155071752584</v>
+        <v>0.8821550717525837</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.9213947595222037</v>
+        <v>0.9213947595222036</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.9245908525940709</v>
+        <v>0.924590852594071</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.04875446643255474</v>
+        <v>-0.04875446643255477</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.528120381546052</v>
+        <v>-0.5281203815460521</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.9727323726665236</v>
+        <v>0.9727323726665235</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7323354517934471</v>
+        <v>0.7323354517934469</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.9387537962313709</v>
+        <v>0.9387537962313708</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.3157484704233943</v>
+        <v>0.3157484704233938</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.924828774024434</v>
+        <v>0.9248287740244342</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.9727709843929451</v>
+        <v>0.9727709843929452</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.5924291647928571</v>
+        <v>-0.5924291647928572</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.8018219572007623</v>
+        <v>0.8018219572007622</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.9503914439508578</v>
+        <v>0.9503914439508576</v>
       </c>
       <c r="BU4" t="n">
         <v>0.9066629506794417</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.916999950260958</v>
+        <v>0.9169999502609578</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.6673896168044728</v>
+        <v>0.6673896168044733</v>
       </c>
       <c r="BX4" t="n">
         <v>0.9509133515158618</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.9738106745488313</v>
+        <v>0.9738106745488315</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.4626164406141984</v>
+        <v>-0.4626164406141983</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.8622643225785576</v>
+        <v>0.8622643225785577</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.9776776387908076</v>
+        <v>0.9776776387908075</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.7642216527557295</v>
+        <v>0.7642216527557296</v>
       </c>
       <c r="CD4" t="n">
         <v>0.8763994293746993</v>
@@ -2229,139 +2229,139 @@
         <v>0.9632019242677679</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.3872248535285332</v>
+        <v>0.3872248535285329</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.9439542560015051</v>
+        <v>0.9439542560015053</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.9595679337052471</v>
+        <v>0.959567933705247</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.2272322885511015</v>
+        <v>0.2272322885511019</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.9283712664023164</v>
+        <v>0.9283712664023152</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.937339515339557</v>
+        <v>0.9373395153395568</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.867880073399919</v>
+        <v>0.8678800733999179</v>
       </c>
       <c r="CN4" t="n">
         <v>0.9604675300148713</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.6287743910681356</v>
+        <v>0.6287743910681355</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.5817143314664567</v>
+        <v>0.5817143314664569</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.005565468284516047</v>
+        <v>-0.005565468284514853</v>
       </c>
       <c r="CR4" t="n">
         <v>0.9529422836128572</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.9712512579576741</v>
+        <v>0.9712512579576742</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.9508399823126815</v>
+        <v>0.9508399823126814</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.9438211890287102</v>
+        <v>0.9438211890287103</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.9284363738093528</v>
+        <v>0.9284363738093531</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.9138882032004142</v>
+        <v>0.9138882032004141</v>
       </c>
       <c r="CX4" t="n">
         <v>0.9193861670066535</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.9443305329218473</v>
+        <v>0.9443305329218469</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.8946628715469485</v>
+        <v>0.8946628715469487</v>
       </c>
       <c r="DA4" t="n">
         <v>0.9176751762654962</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.8511065941960311</v>
+        <v>0.8511065941960305</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.9278735499997123</v>
+        <v>0.9278735499997122</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.9252152400129977</v>
+        <v>0.9252152400129979</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.9251073093231537</v>
+        <v>0.9251073093231436</v>
       </c>
       <c r="DF4" t="n">
         <v>0.9128214102602051</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.9189869678963606</v>
+        <v>0.9189869678963608</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.9394438827615137</v>
+        <v>0.9394438827615135</v>
       </c>
       <c r="DI4" t="n">
         <v>0.9396221569535775</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.9148672933738923</v>
+        <v>0.9148672933738926</v>
       </c>
       <c r="DK4" t="n">
         <v>0.9797053758479954</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.8827051365867988</v>
+        <v>0.8827051365867998</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.9667942406555359</v>
+        <v>0.9667942406555357</v>
       </c>
       <c r="DN4" t="n">
         <v>0.9714664760276369</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.8915330259037133</v>
+        <v>0.8915330259037134</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.9927636932368009</v>
+        <v>0.9927636932368007</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.09258792645160099</v>
+        <v>-0.09258792645160258</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.2712886102401551</v>
+        <v>0.2712886102401564</v>
       </c>
       <c r="DS4" t="n">
         <v>0.9692678983826614</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.8604507019697812</v>
+        <v>0.8604507019697814</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.8769224330652183</v>
+        <v>0.8769224330652182</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.899252354063049</v>
+        <v>0.8992523540630498</v>
       </c>
       <c r="DW4" t="n">
         <v>0.9815354598451713</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.84533295630876</v>
+        <v>0.8453329563087602</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.9705785488408197</v>
+        <v>0.9705785488408196</v>
       </c>
       <c r="DZ4" t="n">
         <v>0.9504730562380008</v>
@@ -2373,28 +2373,28 @@
         <v>0.9632195469453961</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.9932657502381457</v>
+        <v>0.9932657502381459</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.08746300376879963</v>
+        <v>0.08746300376879773</v>
       </c>
       <c r="EE4" t="n">
         <v>0.9390413380404083</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0.08380610034911369</v>
+        <v>-0.0838061003491273</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.6644050337009686</v>
+        <v>0.6644050337009677</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.7648630524626472</v>
+        <v>0.7648630524626419</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.8144108678874667</v>
+        <v>0.8144108678874711</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.8256292495769864</v>
+        <v>0.8256292495769869</v>
       </c>
     </row>
     <row r="5">
@@ -2404,244 +2404,244 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9332968088011391</v>
+        <v>0.9332968088011394</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6076066854901532</v>
+        <v>0.6076066854901533</v>
       </c>
       <c r="D5" t="n">
-        <v>0.97270691053115</v>
+        <v>0.9727069105311508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.886212196078968</v>
+        <v>0.9497358239326603</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9272213412003578</v>
+        <v>0.9272213412003583</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9718398680106433</v>
+        <v>0.9718398680106435</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9310226521605464</v>
+        <v>0.9310226521605465</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8972155080666441</v>
+        <v>0.8972155080666443</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9460810346434863</v>
+        <v>0.9063714047005833</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8726926361090379</v>
+        <v>0.8726926361090381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9521563234249355</v>
+        <v>0.9521563234249353</v>
       </c>
       <c r="M5" t="n">
         <v>0.6598786610667637</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6559934284741471</v>
+        <v>0.6559934284741475</v>
       </c>
       <c r="O5" t="n">
         <v>0.7699081025259391</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9406788131156854</v>
+        <v>0.9406788131156859</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7366380255145321</v>
+        <v>0.7366380255145323</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9607032087834719</v>
+        <v>0.9607032087834722</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9690696375938108</v>
+        <v>0.9690696375938106</v>
       </c>
       <c r="T5" t="n">
-        <v>0.971261535043862</v>
+        <v>0.9712615350438619</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9519068366802281</v>
+        <v>0.9519068366802284</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9515463510330104</v>
+        <v>0.9515463510330107</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8543675646054956</v>
+        <v>0.8543675646054953</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9575802168349642</v>
+        <v>0.957580216834964</v>
       </c>
       <c r="Y5" t="n">
         <v>0.9544048982277722</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9278560971188958</v>
+        <v>0.9278560971188961</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9925288272657689</v>
+        <v>0.992528827265769</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9420609943643687</v>
+        <v>0.9420609943643691</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8800490458294112</v>
+        <v>0.8800490458294116</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6866757587818276</v>
+        <v>0.6866757587818288</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8497588013730772</v>
+        <v>0.8497588013730784</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.9776385858658873</v>
+        <v>0.9776385858658874</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.8498646560056602</v>
+        <v>0.8498646560056599</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.9711143163386067</v>
+        <v>0.9711143163386068</v>
       </c>
       <c r="AI5" t="n">
         <v>0.937110791177604</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9608561996133691</v>
+        <v>0.9608561996133693</v>
       </c>
       <c r="AK5" t="n">
         <v>0.8538765041270722</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9284369927822262</v>
+        <v>0.928436992782226</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8901038534176626</v>
+        <v>0.8901038534176624</v>
       </c>
       <c r="AN5" t="n">
         <v>0.9629091518586739</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.8903715495847603</v>
+        <v>0.8903715495847597</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.8263264223258011</v>
+        <v>0.826326422325801</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9590411289742526</v>
+        <v>0.9590411289742529</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9684777828396735</v>
+        <v>0.9684777828396736</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.9600756216611436</v>
+        <v>0.9600756216611438</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.667050684994231</v>
+        <v>0.6670506849942327</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.7683192206780582</v>
+        <v>0.7683192206780598</v>
       </c>
       <c r="AV5" t="n">
         <v>0.9307068246640668</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.9131921943327804</v>
+        <v>0.9131921943327801</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.981575499741862</v>
+        <v>0.9815754997418618</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.994211563357233</v>
+        <v>0.9942115633572332</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.8981306425298132</v>
+        <v>0.8981306425298137</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.7861744486161146</v>
+        <v>0.7861744486161176</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.9410884955998031</v>
+        <v>0.9410884955998033</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.9351301290306764</v>
+        <v>0.9351301290306762</v>
       </c>
       <c r="BD5" t="n">
         <v>0.9056695800937841</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.9481160914818674</v>
+        <v>0.9481160914818673</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.9188208397456269</v>
+        <v>0.9188208397456266</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.882155071752584</v>
+        <v>0.8821550717525837</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.9213947595222037</v>
+        <v>0.9213947595222036</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.9245908525940709</v>
+        <v>0.924590852594071</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.04875446643255474</v>
+        <v>-0.04875446643255477</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.528120381546052</v>
+        <v>-0.5281203815460521</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9727323726665236</v>
+        <v>0.9727323726665235</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7323354517934471</v>
+        <v>0.7323354517934469</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.9387537962313709</v>
+        <v>0.9387537962313708</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.3157484704233943</v>
+        <v>0.3157484704233938</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.924828774024434</v>
+        <v>0.9248287740244342</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.9727709843929451</v>
+        <v>0.9727709843929452</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.5924291647928571</v>
+        <v>-0.5924291647928572</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.8018219572007623</v>
+        <v>0.8018219572007622</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.9503914439508578</v>
+        <v>0.9503914439508576</v>
       </c>
       <c r="BU5" t="n">
         <v>0.9066629506794417</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.916999950260958</v>
+        <v>0.9169999502609578</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.6673896168044728</v>
+        <v>0.6673896168044733</v>
       </c>
       <c r="BX5" t="n">
         <v>0.9509133515158618</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.9738106745488313</v>
+        <v>0.9738106745488315</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.4626164406141984</v>
+        <v>-0.4626164406141983</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.8622643225785576</v>
+        <v>0.8622643225785577</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.9776776387908076</v>
+        <v>0.9776776387908075</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.7642216527557295</v>
+        <v>0.7642216527557296</v>
       </c>
       <c r="CD5" t="n">
         <v>0.8763994293746993</v>
@@ -2653,139 +2653,139 @@
         <v>0.9632019242677679</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.3872248535285332</v>
+        <v>0.3872248535285329</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.9439542560015051</v>
+        <v>0.9439542560015053</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.9595679337052471</v>
+        <v>0.959567933705247</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.2272322885511015</v>
+        <v>0.2272322885511019</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.9283712664023164</v>
+        <v>0.9283712664023152</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.937339515339557</v>
+        <v>0.9373395153395568</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.867880073399919</v>
+        <v>0.8678800733999179</v>
       </c>
       <c r="CN5" t="n">
         <v>0.9604675300148713</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.6287743910681356</v>
+        <v>0.6287743910681355</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.5817143314664567</v>
+        <v>0.5817143314664569</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.005565468284516047</v>
+        <v>-0.005565468284514853</v>
       </c>
       <c r="CR5" t="n">
         <v>0.9529422836128572</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.9712512579576741</v>
+        <v>0.9712512579576742</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.9508399823126815</v>
+        <v>0.9508399823126814</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.9438211890287102</v>
+        <v>0.9438211890287103</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.9284363738093528</v>
+        <v>0.9284363738093531</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.9138882032004142</v>
+        <v>0.9138882032004141</v>
       </c>
       <c r="CX5" t="n">
         <v>0.9193861670066535</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.9443305329218473</v>
+        <v>0.9443305329218469</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.8946628715469485</v>
+        <v>0.8946628715469487</v>
       </c>
       <c r="DA5" t="n">
         <v>0.9176751762654962</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.8511065941960311</v>
+        <v>0.8511065941960305</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.9278735499997123</v>
+        <v>0.9278735499997122</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.9252152400129977</v>
+        <v>0.9252152400129979</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.9251073093231537</v>
+        <v>0.9251073093231436</v>
       </c>
       <c r="DF5" t="n">
         <v>0.9128214102602051</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.9189869678963606</v>
+        <v>0.9189869678963608</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.9394438827615137</v>
+        <v>0.9394438827615135</v>
       </c>
       <c r="DI5" t="n">
         <v>0.9396221569535775</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.9148672933738923</v>
+        <v>0.9148672933738926</v>
       </c>
       <c r="DK5" t="n">
         <v>0.9797053758479954</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.8827051365867988</v>
+        <v>0.8827051365867998</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.9667942406555359</v>
+        <v>0.9667942406555357</v>
       </c>
       <c r="DN5" t="n">
         <v>0.9714664760276369</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.8915330259037133</v>
+        <v>0.8915330259037134</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.9927636932368009</v>
+        <v>0.9927636932368007</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.09258792645160099</v>
+        <v>-0.09258792645160258</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2712886102401551</v>
+        <v>0.2712886102401564</v>
       </c>
       <c r="DS5" t="n">
         <v>0.9692678983826614</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.8604507019697812</v>
+        <v>0.8604507019697814</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.8769224330652183</v>
+        <v>0.8769224330652182</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.899252354063049</v>
+        <v>0.8992523540630498</v>
       </c>
       <c r="DW5" t="n">
         <v>0.9815354598451713</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.84533295630876</v>
+        <v>0.8453329563087602</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.9705785488408197</v>
+        <v>0.9705785488408196</v>
       </c>
       <c r="DZ5" t="n">
         <v>0.9504730562380008</v>
@@ -2797,28 +2797,28 @@
         <v>0.9632195469453961</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.9932657502381457</v>
+        <v>0.9932657502381459</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.08746300376879963</v>
+        <v>0.08746300376879773</v>
       </c>
       <c r="EE5" t="n">
         <v>0.9390413380404083</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.08380610034911369</v>
+        <v>-0.0838061003491273</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.6644050337009686</v>
+        <v>0.6644050337009677</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.7648630524626472</v>
+        <v>0.7648630524626419</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.8144108678874667</v>
+        <v>0.8144108678874711</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.8256292495769864</v>
+        <v>0.8256292495769869</v>
       </c>
     </row>
     <row r="6">
@@ -2828,103 +2828,103 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9465658744168638</v>
+        <v>0.9465658744168644</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6554695775499599</v>
+        <v>0.6554695775499602</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9700722731911148</v>
+        <v>0.9700722731911159</v>
       </c>
       <c r="E6" t="n">
-        <v>0.904504768493907</v>
+        <v>0.9353541710803663</v>
       </c>
       <c r="F6" t="n">
-        <v>0.942935231758991</v>
+        <v>0.9429352317589914</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9799759325081149</v>
+        <v>0.9799759325081151</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9399226044954206</v>
+        <v>0.9399226044954208</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9152347870527539</v>
+        <v>0.915234787052754</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9589739177463011</v>
+        <v>0.8774080481339174</v>
       </c>
       <c r="K6" t="n">
-        <v>0.885908513025655</v>
+        <v>0.8859085130256551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9447113998358119</v>
+        <v>0.9447113998358114</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6251336272510962</v>
+        <v>0.625133627251096</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6756843287344448</v>
+        <v>0.6756843287344453</v>
       </c>
       <c r="O6" t="n">
         <v>0.7428222931443809</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9290032841958038</v>
+        <v>0.9290032841958044</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7062283212028524</v>
+        <v>0.7062283212028526</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9546028115847101</v>
+        <v>0.9546028115847103</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9565744639552256</v>
+        <v>0.9565744639552258</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9680425500120345</v>
+        <v>0.9680425500120344</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9387917292359698</v>
+        <v>0.9387917292359699</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9412636112281286</v>
+        <v>0.9412636112281287</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8563424955839702</v>
+        <v>0.8563424955839699</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9484177692520886</v>
+        <v>0.9484177692520883</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9499913007425275</v>
+        <v>0.9499913007425272</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9108096738877841</v>
+        <v>0.9108096738877843</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.9904277312784349</v>
+        <v>0.9904277312784351</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9478896494757958</v>
+        <v>0.947889649475796</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.900329665431006</v>
+        <v>0.9003296654310063</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.7174108021070956</v>
+        <v>0.717410802107097</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.8667628737089942</v>
+        <v>0.8667628737089951</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.9839032033744153</v>
+        <v>0.9839032033744152</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.8587222123384749</v>
+        <v>0.8587222123384748</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.9662195538328044</v>
+        <v>0.9662195538328043</v>
       </c>
       <c r="AI6" t="n">
         <v>0.9289726770260827</v>
@@ -2936,82 +2936,82 @@
         <v>0.8313510067766117</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.9443721419613166</v>
+        <v>0.9443721419613164</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.9091010902954859</v>
+        <v>0.9091010902954857</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.961170654962655</v>
+        <v>0.9611706549626549</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.8824583330271211</v>
+        <v>0.8824583330271203</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.8177373593941621</v>
+        <v>0.8177373593941619</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.9499141660461877</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.9649181749128828</v>
+        <v>0.9649181749128827</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.9570349053955437</v>
+        <v>0.9570349053955438</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.6496215365147739</v>
+        <v>0.6496215365147755</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.7965950489849368</v>
+        <v>0.7965950489849384</v>
       </c>
       <c r="AV6" t="n">
         <v>0.9361484226551716</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.8943151110064194</v>
+        <v>0.8943151110064188</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.9820078701628624</v>
+        <v>0.9820078701628623</v>
       </c>
       <c r="AY6" t="n">
         <v>0.9932168563428366</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.8774651375018874</v>
+        <v>0.8774651375018875</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.8196746644657547</v>
+        <v>0.8196746644657575</v>
       </c>
       <c r="BB6" t="n">
         <v>0.9609208934241893</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.9208788767019676</v>
+        <v>0.9208788767019673</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.8787451313791913</v>
+        <v>0.8787451313791912</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.9558045088404774</v>
+        <v>0.9558045088404773</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.9211700521576579</v>
+        <v>0.9211700521576573</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.8671659179826603</v>
+        <v>0.8671659179826601</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.8900481533709408</v>
+        <v>0.8900481533709409</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.9314426324895804</v>
+        <v>0.9314426324895805</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.05912038000589598</v>
+        <v>-0.05912038000589595</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.4710908592506215</v>
+        <v>-0.4710908592506217</v>
       </c>
       <c r="BL6" t="n">
         <v>0.9655152940097492</v>
@@ -3020,229 +3020,229 @@
         <v>0.7770121686238145</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.9333715543970125</v>
+        <v>0.9333715543970122</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.3783003000372924</v>
+        <v>0.3783003000372921</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.9164927240841575</v>
+        <v>0.9164927240841576</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.9621932821616747</v>
+        <v>0.9621932821616748</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.5233626788495305</v>
+        <v>-0.5233626788495307</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.7977018497950423</v>
+        <v>0.7977018497950422</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.9507328605398297</v>
+        <v>0.9507328605398296</v>
       </c>
       <c r="BU6" t="n">
         <v>0.8997583852701093</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.915592903711887</v>
+        <v>0.9155929037118868</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.6624108808796157</v>
+        <v>0.6624108808796167</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.9496717336822637</v>
+        <v>0.9496717336822635</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.9642126613113384</v>
+        <v>0.9642126613113388</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.4289410620182653</v>
+        <v>-0.4289410620182651</v>
       </c>
       <c r="CA6" t="n">
         <v>0.8742822521828469</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.9715969792962262</v>
+        <v>0.971596979296226</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.7972609341902238</v>
+        <v>0.7972609341902239</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.8568348134638535</v>
+        <v>0.8568348134638534</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.926130908986049</v>
+        <v>0.9261309089860489</v>
       </c>
       <c r="CF6" t="n">
         <v>0.9515612083976543</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.3417120703998122</v>
+        <v>0.341712070399812</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.9338356940506415</v>
+        <v>0.9338356940506418</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.9476564641172305</v>
+        <v>0.9476564641172303</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.2152872010405794</v>
+        <v>0.2152872010405796</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.9266787728686148</v>
+        <v>0.9266787728686134</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.9450985509492728</v>
+        <v>0.9450985509492729</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.8728741765926397</v>
+        <v>0.8728741765926383</v>
       </c>
       <c r="CN6" t="n">
         <v>0.959790407239369</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.6274174829054482</v>
+        <v>0.6274174829054481</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.6221419848725469</v>
+        <v>0.622141984872547</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.002108997764712586</v>
+        <v>0.00210899776471369</v>
       </c>
       <c r="CR6" t="n">
         <v>0.9396152847212789</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.9635969459154166</v>
+        <v>0.9635969459154168</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.9392249309472555</v>
+        <v>0.9392249309472552</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.9249142880111796</v>
+        <v>0.9249142880111797</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.9310021390745338</v>
+        <v>0.9310021390745339</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.9127396994215482</v>
+        <v>0.9127396994215481</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.9184551721219125</v>
+        <v>0.9184551721219124</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.9391800814182951</v>
+        <v>0.9391800814182948</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.8923387961602322</v>
+        <v>0.8923387961602323</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.9110916127402564</v>
+        <v>0.9110916127402565</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.8417226255248511</v>
+        <v>0.8417226255248504</v>
       </c>
       <c r="DC6" t="n">
         <v>0.9199716566720988</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.9222626169283561</v>
+        <v>0.9222626169283563</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.9160380645329691</v>
+        <v>0.9160380645329577</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.9009110875477142</v>
+        <v>0.9009110875477143</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.9267767737906534</v>
+        <v>0.9267767737906536</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.9469379547583208</v>
+        <v>0.9469379547583205</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.9398255384554355</v>
+        <v>0.9398255384554357</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.9113941506399074</v>
+        <v>0.9113941506399081</v>
       </c>
       <c r="DK6" t="n">
         <v>0.9745652614406914</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.8916732079801301</v>
+        <v>0.8916732079801308</v>
       </c>
       <c r="DM6" t="n">
         <v>0.9550663843678195</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9615423111607655</v>
+        <v>0.9615423111607654</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.8588036017636805</v>
+        <v>0.8588036017636806</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.9907194390990344</v>
+        <v>0.9907194390990345</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.02505879883103154</v>
+        <v>-0.0250587988310334</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.2636921149360769</v>
+        <v>0.2636921149360781</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.9727681554410219</v>
+        <v>0.972768155441022</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.8550178409258823</v>
+        <v>0.8550178409258824</v>
       </c>
       <c r="DU6" t="n">
         <v>0.8690814487179166</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.8935323863910392</v>
+        <v>0.8935323863910398</v>
       </c>
       <c r="DW6" t="n">
         <v>0.9725963293909398</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.8554340707850518</v>
+        <v>0.855434070785052</v>
       </c>
       <c r="DY6" t="n">
         <v>0.9691774306324424</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.9565908229880936</v>
+        <v>0.9565908229880937</v>
       </c>
       <c r="EA6" t="n">
         <v>0.9580588339319798</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.9539876903472188</v>
+        <v>0.9539876903472186</v>
       </c>
       <c r="EC6" t="n">
         <v>0.9850477336719572</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.078637635366282</v>
+        <v>0.07863763536627955</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.9593880372568185</v>
+        <v>0.9593880372568184</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.1178545794697968</v>
+        <v>-0.1178545794698118</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.6189827585967743</v>
+        <v>0.6189827585967734</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.7615059963129409</v>
+        <v>0.7615059963129356</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.8113842664185886</v>
+        <v>0.8113842664185924</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.845158046184326</v>
+        <v>0.8451580461843267</v>
       </c>
     </row>
     <row r="7">
@@ -3252,100 +3252,100 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.918432766415283</v>
+        <v>0.9184327664152834</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6069447630466477</v>
+        <v>0.6069447630466478</v>
       </c>
       <c r="D7" t="n">
-        <v>0.973418014483187</v>
+        <v>0.9734180144831878</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8578671114841971</v>
+        <v>0.9658023255724815</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9068897681311046</v>
+        <v>0.906889768131105</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9591834301350118</v>
+        <v>0.9591834301350119</v>
       </c>
       <c r="H7" t="n">
         <v>0.9095311258025257</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8683875261031193</v>
+        <v>0.8683875261031195</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9283448279657387</v>
+        <v>0.9307358021371031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8434214673875849</v>
+        <v>0.8434214673875852</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9638513967014312</v>
+        <v>0.9638513967014311</v>
       </c>
       <c r="M7" t="n">
         <v>0.7162865603733003</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6563984951475531</v>
+        <v>0.6563984951475534</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7808378741060311</v>
+        <v>0.780837874106031</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9572743591491744</v>
+        <v>0.9572743591491746</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7771370680802556</v>
+        <v>0.7771370680802558</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9592044292229105</v>
+        <v>0.9592044292229107</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9786494210515393</v>
+        <v>0.9786494210515395</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9778908484378485</v>
+        <v>0.9778908484378481</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9655605931855289</v>
+        <v>0.9655605931855291</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9640425353506106</v>
+        <v>0.9640425353506104</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8321833456000226</v>
+        <v>0.8321833456000223</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9715625972414386</v>
+        <v>0.9715625972414383</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9576040776832004</v>
+        <v>0.9576040776832002</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9438091534764359</v>
+        <v>0.9438091534764363</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9848123046582944</v>
+        <v>0.9848123046582945</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9511358429491715</v>
+        <v>0.9511358429491716</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8809831004893937</v>
+        <v>0.8809831004893941</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.6869749804636878</v>
+        <v>0.686974980463689</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.8607220339059992</v>
+        <v>0.8607220339060003</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.9652365008652966</v>
+        <v>0.9652365008652964</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.8444556558487217</v>
+        <v>0.8444556558487215</v>
       </c>
       <c r="AH7" t="n">
         <v>0.9705166433520345</v>
@@ -3354,28 +3354,28 @@
         <v>0.9448484093402439</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.9695710998807283</v>
+        <v>0.9695710998807284</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.8781997954557936</v>
+        <v>0.8781997954557937</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.9343636014993288</v>
+        <v>0.9343636014993285</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.8976593990526023</v>
+        <v>0.8976593990526018</v>
       </c>
       <c r="AN7" t="n">
         <v>0.9682950472674254</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.8953319140070801</v>
+        <v>0.8953319140070795</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.8377349094347533</v>
+        <v>0.8377349094347531</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.9708844941167745</v>
+        <v>0.9708844941167747</v>
       </c>
       <c r="AR7" t="n">
         <v>0.9771259407498905</v>
@@ -3384,34 +3384,34 @@
         <v>0.964401207463163</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.6916587363297804</v>
+        <v>0.6916587363297819</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.7705481674465349</v>
+        <v>0.7705481674465364</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.9208160056708947</v>
+        <v>0.9208160056708945</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.9398208053782822</v>
+        <v>0.9398208053782818</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.9848313151203132</v>
+        <v>0.9848313151203127</v>
       </c>
       <c r="AY7" t="n">
         <v>0.9860409801988712</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.921735001684122</v>
+        <v>0.9217350016841221</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.7900120581268288</v>
+        <v>0.790012058126832</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.9181879711134915</v>
+        <v>0.9181879711134916</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.9349835535427635</v>
+        <v>0.9349835535427633</v>
       </c>
       <c r="BD7" t="n">
         <v>0.9287472069311862</v>
@@ -3420,73 +3420,73 @@
         <v>0.9471341378587128</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.9340218587249562</v>
+        <v>0.9340218587249559</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.8976227857279805</v>
+        <v>0.8976227857279802</v>
       </c>
       <c r="BH7" t="n">
         <v>0.9388167512276455</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.9215378693780364</v>
+        <v>0.9215378693780365</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.07192027989037567</v>
+        <v>-0.07192027989037575</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.5689241572561504</v>
+        <v>-0.5689241572561505</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9746600278370323</v>
+        <v>0.9746600278370324</v>
       </c>
       <c r="BM7" t="n">
         <v>0.7173640593867024</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.9528757014361829</v>
+        <v>0.9528757014361831</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.2987173823198628</v>
+        <v>0.2987173823198623</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.9425001761130753</v>
+        <v>0.9425001761130759</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.9708384269900951</v>
+        <v>0.9708384269900953</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.6195613961384748</v>
+        <v>-0.6195613961384751</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.8083453473359807</v>
+        <v>0.8083453473359806</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.95656721850467</v>
+        <v>0.9565672185046699</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.9236745654587474</v>
+        <v>0.9236745654587475</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.9185983146656926</v>
+        <v>0.9185983146656925</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.6637141995634238</v>
+        <v>0.663714199563425</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.9609024756385046</v>
+        <v>0.9609024756385045</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.9871938966868915</v>
+        <v>0.9871938966868916</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.4430606012755818</v>
+        <v>-0.4430606012755816</v>
       </c>
       <c r="CA7" t="n">
         <v>0.8812315137292048</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.9782203164341621</v>
+        <v>0.9782203164341619</v>
       </c>
       <c r="CC7" t="n">
         <v>0.7498523019068177</v>
@@ -3498,28 +3498,28 @@
         <v>0.9614468056340526</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.9670693825585372</v>
+        <v>0.9670693825585375</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.456428176091014</v>
+        <v>0.4564281760910139</v>
       </c>
       <c r="CH7" t="n">
         <v>0.9556514476456763</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.9554894928828322</v>
+        <v>0.9554894928828321</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.2846121174521711</v>
+        <v>0.2846121174521713</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.9409594477917047</v>
+        <v>0.9409594477917036</v>
       </c>
       <c r="CL7" t="n">
         <v>0.9363799925580881</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.8802226868938041</v>
+        <v>0.8802226868938032</v>
       </c>
       <c r="CN7" t="n">
         <v>0.9682757956061816</v>
@@ -3531,73 +3531,73 @@
         <v>0.591399271300755</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.01840782913204735</v>
+        <v>0.01840782913204857</v>
       </c>
       <c r="CR7" t="n">
         <v>0.9628872217806421</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.9854409834385799</v>
+        <v>0.98544098343858</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.9692431123140084</v>
+        <v>0.9692431123140083</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.9631247710352389</v>
+        <v>0.963124771035239</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.9390795307371018</v>
+        <v>0.9390795307371019</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.9215671245671531</v>
+        <v>0.921567124567153</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.9059081354487919</v>
+        <v>0.9059081354487921</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.9541691783735057</v>
+        <v>0.9541691783735055</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.9154133729807727</v>
+        <v>0.9154133729807729</v>
       </c>
       <c r="DA7" t="n">
         <v>0.9350731084740251</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.8584132329689456</v>
+        <v>0.8584132329689451</v>
       </c>
       <c r="DC7" t="n">
         <v>0.9032947522950701</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.9411377648215296</v>
+        <v>0.9411377648215298</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.9345015800191511</v>
+        <v>0.9345015800191412</v>
       </c>
       <c r="DF7" t="n">
         <v>0.906451161153995</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.9200818496383043</v>
+        <v>0.9200818496383044</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.9389621970601794</v>
+        <v>0.9389621970601789</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.9393484549382995</v>
+        <v>0.9393484549382997</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.9259650362757812</v>
+        <v>0.925965036275781</v>
       </c>
       <c r="DK7" t="n">
         <v>0.9882076479728886</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.8928988281542968</v>
+        <v>0.892898828154298</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.9661381660980881</v>
+        <v>0.9661381660980879</v>
       </c>
       <c r="DN7" t="n">
         <v>0.9834212115421563</v>
@@ -3606,13 +3606,13 @@
         <v>0.9198081995269385</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.9840024027118555</v>
+        <v>0.9840024027118554</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1175704129890289</v>
+        <v>-0.1175704129890304</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.3068461414831722</v>
+        <v>0.3068461414831735</v>
       </c>
       <c r="DS7" t="n">
         <v>0.9697855819053436</v>
@@ -3624,16 +3624,16 @@
         <v>0.8970691231104535</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.8998307235269519</v>
+        <v>0.8998307235269527</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.991972997397143</v>
+        <v>0.9919729973971431</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.8614317328737108</v>
+        <v>0.861431732873711</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.9738236900639254</v>
+        <v>0.9738236900639252</v>
       </c>
       <c r="DZ7" t="n">
         <v>0.9581506693516344</v>
@@ -3642,31 +3642,31 @@
         <v>0.9804967371130918</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.9763617521216631</v>
+        <v>0.976361752121663</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.9926164560408774</v>
+        <v>0.9926164560408773</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.07453986905915963</v>
+        <v>0.07453986905915799</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.9411982676943154</v>
+        <v>0.9411982676943151</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.03955911187232793</v>
+        <v>-0.03955911187234248</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.7035420772764744</v>
+        <v>0.7035420772764738</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.7876757606357235</v>
+        <v>0.7876757606357189</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.8314884237988557</v>
+        <v>0.8314884237988595</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.8366264062786051</v>
+        <v>0.8366264062786057</v>
       </c>
     </row>
     <row r="8">
@@ -3676,187 +3676,187 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8904260015155256</v>
+        <v>0.890426001515526</v>
       </c>
       <c r="C8" t="n">
-        <v>0.534142944796431</v>
+        <v>0.5341429447964309</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9541527989601563</v>
+        <v>0.9541527989601568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8380189648716801</v>
+        <v>0.9530096982842362</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8788106557441947</v>
+        <v>0.878810655744195</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9357450107118602</v>
+        <v>0.9357450107118606</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8954349472700436</v>
+        <v>0.8954349472700437</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8494982309474048</v>
+        <v>0.8494982309474051</v>
       </c>
       <c r="J8" t="n">
-        <v>0.904271368125229</v>
+        <v>0.9454441574946959</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8309176255595827</v>
+        <v>0.8309176255595828</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9468456097946041</v>
+        <v>0.9468456097946042</v>
       </c>
       <c r="M8" t="n">
         <v>0.7176175850664954</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6065268026930635</v>
+        <v>0.606526802693064</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7959851107520773</v>
+        <v>0.7959851107520775</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9478797652585043</v>
+        <v>0.9478797652585045</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.77879256887605</v>
+        <v>0.7787925688760501</v>
       </c>
       <c r="R8" t="n">
         <v>0.9496298995252799</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9712682420678556</v>
+        <v>0.9712682420678553</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9585153213947614</v>
+        <v>0.9585153213947615</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9614078855443301</v>
+        <v>0.9614078855443302</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9514539757545273</v>
+        <v>0.9514539757545275</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8312070950766145</v>
+        <v>0.8312070950766143</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9526485701693622</v>
+        <v>0.9526485701693621</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9426831617974983</v>
+        <v>0.9426831617974982</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9443299078338238</v>
+        <v>0.9443299078338239</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9687833741236079</v>
+        <v>0.9687833741236083</v>
       </c>
       <c r="AB8" t="n">
         <v>0.9147953360349053</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.828599335373759</v>
+        <v>0.8285993353737595</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.6284351691523905</v>
+        <v>0.6284351691523919</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8092730188236934</v>
+        <v>0.8092730188236951</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.9415105048063732</v>
+        <v>0.9415105048063734</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.8038107038440021</v>
+        <v>0.8038107038440017</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.9591358025361474</v>
+        <v>0.9591358025361473</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.9309925797943943</v>
+        <v>0.9309925797943945</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.9386389376865814</v>
+        <v>0.9386389376865812</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.8809936242692622</v>
+        <v>0.8809936242692624</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.8857158206915563</v>
+        <v>0.8857158206915559</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.8445720101185963</v>
+        <v>0.8445720101185962</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.9520918383271941</v>
+        <v>0.9520918383271942</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.8834515284792568</v>
+        <v>0.8834515284792561</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.8258696383533497</v>
+        <v>0.8258696383533496</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.9561865634409541</v>
+        <v>0.9561865634409543</v>
       </c>
       <c r="AR8" t="n">
         <v>0.9542834558069991</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.9429680911343254</v>
+        <v>0.9429680911343253</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.6923358048867713</v>
+        <v>0.692335804886773</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.726926472448831</v>
+        <v>0.7269264724488327</v>
       </c>
       <c r="AV8" t="n">
         <v>0.8978581784431723</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.9262020126725177</v>
+        <v>0.9262020126725174</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.9590747867811227</v>
+        <v>0.9590747867811225</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.9709470902274083</v>
+        <v>0.9709470902274085</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.9188331476851402</v>
+        <v>0.9188331476851405</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.7221525297753104</v>
+        <v>0.7221525297753139</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.8866005632658026</v>
+        <v>0.8866005632658025</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.9415762189858682</v>
+        <v>0.9415762189858681</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.9319857553817424</v>
+        <v>0.9319857553817426</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.9144328800403587</v>
+        <v>0.9144328800403586</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.8988286886056617</v>
+        <v>0.8988286886056615</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.8931813114868753</v>
+        <v>0.8931813114868752</v>
       </c>
       <c r="BH8" t="n">
         <v>0.9591209353236499</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.9035463776241968</v>
+        <v>0.9035463776241969</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0.06045832874098736</v>
+        <v>-0.06045832874098747</v>
       </c>
       <c r="BK8" t="n">
         <v>-0.6042701014662399</v>
@@ -3868,34 +3868,34 @@
         <v>0.6495885472264286</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.9370631354136953</v>
+        <v>0.9370631354136952</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.2123205503524337</v>
+        <v>0.212320550352433</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.9283622453951259</v>
+        <v>0.9283622453951264</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.9662909335523167</v>
+        <v>0.9662909335523169</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.6881390082102309</v>
+        <v>-0.688139008210231</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.7959365281294148</v>
+        <v>0.7959365281294147</v>
       </c>
       <c r="BT8" t="n">
         <v>0.9312306852612617</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.9065008892396438</v>
+        <v>0.9065008892396437</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9036767078863233</v>
+        <v>0.9036767078863231</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.662146719549275</v>
+        <v>0.6621467195492747</v>
       </c>
       <c r="BX8" t="n">
         <v>0.9344547426895887</v>
@@ -3904,91 +3904,91 @@
         <v>0.970724469178658</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.4911483339230966</v>
+        <v>-0.4911483339230963</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.831333174001856</v>
+        <v>0.8313331740018559</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.9671360367448657</v>
+        <v>0.9671360367448656</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.69331968950639</v>
+        <v>0.6933196895063903</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.8823223051102441</v>
+        <v>0.882322305110244</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.9567156859055638</v>
+        <v>0.9567156859055637</v>
       </c>
       <c r="CF8" t="n">
         <v>0.9547748905893026</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.474405566212044</v>
+        <v>0.4744055662120438</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.9425305865567669</v>
+        <v>0.942530586556767</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.9567767560339081</v>
+        <v>0.9567767560339079</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.2590663404904954</v>
+        <v>0.2590663404904957</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.9066701204932721</v>
+        <v>0.9066701204932713</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.9017997039427119</v>
+        <v>0.901799703942712</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.8391787615094625</v>
+        <v>0.8391787615094612</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.9509445913512178</v>
+        <v>0.9509445913512177</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.5942064511117612</v>
+        <v>0.5942064511117611</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.5154556717455727</v>
+        <v>0.5154556717455728</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.01620280727228162</v>
+        <v>-0.0162028072722803</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.9586841145573437</v>
+        <v>0.9586841145573438</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.9618162260104806</v>
+        <v>0.9618162260104807</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.9531333376548827</v>
+        <v>0.9531333376548825</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.9542563755917749</v>
+        <v>0.9542563755917751</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.9094231360200419</v>
+        <v>0.909423136020042</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.9043540085666556</v>
+        <v>0.9043540085666555</v>
       </c>
       <c r="CX8" t="n">
         <v>0.8979368388130218</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.9453574060665902</v>
+        <v>0.9453574060665901</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.888133316055389</v>
+        <v>0.8881333160553891</v>
       </c>
       <c r="DA8" t="n">
         <v>0.9158616502617258</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.8442009959130951</v>
+        <v>0.8442009959130943</v>
       </c>
       <c r="DC8" t="n">
         <v>0.9295308783281309</v>
@@ -3997,34 +3997,34 @@
         <v>0.917116934527494</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.9203131242611348</v>
+        <v>0.920313124261124</v>
       </c>
       <c r="DF8" t="n">
         <v>0.9010040177195311</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.8901895949243306</v>
+        <v>0.8901895949243307</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.9044922341291786</v>
+        <v>0.9044922341291783</v>
       </c>
       <c r="DI8" t="n">
         <v>0.9182506603153719</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.9098177986202216</v>
+        <v>0.9098177986202205</v>
       </c>
       <c r="DK8" t="n">
         <v>0.9706296717006295</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.8583528071933395</v>
+        <v>0.8583528071933407</v>
       </c>
       <c r="DM8" t="n">
         <v>0.9641826201144696</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.9719810109665751</v>
+        <v>0.971981010966575</v>
       </c>
       <c r="DO8" t="n">
         <v>0.9253989025043494</v>
@@ -4033,64 +4033,64 @@
         <v>0.9703673670438286</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.1921876308961943</v>
+        <v>-0.1921876308961964</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.2760561405210715</v>
+        <v>0.2760561405210729</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.9411199306965432</v>
+        <v>0.9411199306965434</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.8466506636219608</v>
+        <v>0.8466506636219611</v>
       </c>
       <c r="DU8" t="n">
         <v>0.8802359475669257</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.9047615592254369</v>
+        <v>0.9047615592254377</v>
       </c>
       <c r="DW8" t="n">
         <v>0.9799666144728689</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.8223774489081538</v>
+        <v>0.8223774489081539</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.958542332586913</v>
+        <v>0.9585423325869128</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.9250865437571009</v>
+        <v>0.9250865437571011</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.9664431027210635</v>
+        <v>0.9664431027210634</v>
       </c>
       <c r="EB8" t="n">
         <v>0.962485518124676</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.983671332377149</v>
+        <v>0.9836713323771492</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.08255693163841697</v>
+        <v>0.0825569316384157</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.890792983566669</v>
+        <v>0.8907929835666691</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0.009455131003422686</v>
+        <v>-0.009455131003431205</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.7215094378735998</v>
+        <v>0.7215094378735991</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.7687251082193483</v>
+        <v>0.7687251082193437</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.8161409383673399</v>
+        <v>0.8161409383673447</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.7802477471068459</v>
+        <v>0.7802477471068466</v>
       </c>
     </row>
     <row r="9">
@@ -4100,73 +4100,73 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8979051367505093</v>
+        <v>0.8979051367505098</v>
       </c>
       <c r="C9" t="n">
         <v>0.5727313243455658</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9323780871423122</v>
+        <v>0.9323780871423129</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8341647404158672</v>
+        <v>0.894677960965204</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8877359875393297</v>
+        <v>0.88773598753933</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9343566938267064</v>
+        <v>0.9343566938267069</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8868835456538093</v>
+        <v>0.8868835456538096</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8474169637681508</v>
+        <v>0.847416963768151</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9043065752946923</v>
+        <v>0.8799622811086412</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8206426150590984</v>
+        <v>0.8206426150590986</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9178176245387675</v>
+        <v>0.9178176245387677</v>
       </c>
       <c r="M9" t="n">
-        <v>0.627787373986887</v>
+        <v>0.6277873739868871</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6547038139576945</v>
+        <v>0.6547038139576949</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7280765565730271</v>
+        <v>0.7280765565730269</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9191433562277094</v>
+        <v>0.9191433562277097</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.737195573618173</v>
+        <v>0.7371955736181728</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9425401647113836</v>
+        <v>0.9425401647113835</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9345037680762884</v>
+        <v>0.934503768076288</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9310935239667931</v>
+        <v>0.931093523966793</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8958170904058722</v>
+        <v>0.8958170904058725</v>
       </c>
       <c r="V9" t="n">
         <v>0.9238012506176942</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8047232216787574</v>
+        <v>0.8047232216787572</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9063270100403289</v>
+        <v>0.9063270100403287</v>
       </c>
       <c r="Y9" t="n">
         <v>0.9270076350242018</v>
@@ -4178,37 +4178,37 @@
         <v>0.9548851829543694</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9031178759133063</v>
+        <v>0.9031178759133065</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.8690476845732644</v>
+        <v>0.8690476845732649</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6012676709818298</v>
+        <v>0.6012676709818311</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.8555838603177478</v>
+        <v>0.8555838603177487</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.9404986560040306</v>
+        <v>0.9404986560040305</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.7781716615892217</v>
+        <v>0.7781716615892211</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.9300562315915319</v>
+        <v>0.9300562315915322</v>
       </c>
       <c r="AI9" t="n">
         <v>0.8878094422850287</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.9159757577607308</v>
+        <v>0.9159757577607309</v>
       </c>
       <c r="AK9" t="n">
         <v>0.8229098193748646</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.8940699060788673</v>
+        <v>0.8940699060788669</v>
       </c>
       <c r="AM9" t="n">
         <v>0.8766569264187245</v>
@@ -4217,52 +4217,52 @@
         <v>0.9271385619634134</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8504459533010595</v>
+        <v>0.8504459533010589</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.8088142353279122</v>
+        <v>0.8088142353279117</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.9190514224183297</v>
+        <v>0.9190514224183296</v>
       </c>
       <c r="AR9" t="n">
         <v>0.9252337831996447</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.917112147959073</v>
+        <v>0.9171121479590731</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.6960868204993971</v>
+        <v>0.6960868204993993</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.7708783672928052</v>
+        <v>0.7708783672928067</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.9069155183419977</v>
+        <v>0.9069155183419978</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.8613099266588272</v>
+        <v>0.8613099266588271</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.9398655331335</v>
+        <v>0.9398655331334995</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.9562676012010385</v>
+        <v>0.9562676012010387</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.8659316308841978</v>
+        <v>0.8659316308841982</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.7722357728570278</v>
+        <v>0.772235772857031</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.9108753391859632</v>
+        <v>0.9108753391859628</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.8904074818593419</v>
+        <v>0.8904074818593414</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.8764212087805014</v>
+        <v>0.8764212087805013</v>
       </c>
       <c r="BE9" t="n">
         <v>0.9302333756462489</v>
@@ -4271,160 +4271,160 @@
         <v>0.8820200212226634</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.8476878775680369</v>
+        <v>0.8476878775680367</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.8916606533252188</v>
+        <v>0.8916606533252187</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.8861549436460083</v>
+        <v>0.8861549436460082</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.1157934863865971</v>
+        <v>0.1157934863865972</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.4906304036158039</v>
+        <v>-0.490630403615804</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.9219668696596504</v>
+        <v>0.92196686965965</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.7250934482546414</v>
+        <v>0.7250934482546415</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.8717476096623418</v>
+        <v>0.8717476096623415</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.2947233000115805</v>
+        <v>0.2947233000115803</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.8844181292514235</v>
+        <v>0.8844181292514237</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.9185229873497772</v>
+        <v>0.9185229873497777</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0.5301100087785375</v>
+        <v>-0.5301100087785376</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.8098932601881736</v>
+        <v>0.8098932601881739</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.9188821323160832</v>
+        <v>0.9188821323160831</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.865584607158286</v>
+        <v>0.8655846071582857</v>
       </c>
       <c r="BV9" t="n">
         <v>0.8857244140225906</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.7371530136010659</v>
+        <v>0.7371530136010648</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.9073643910721301</v>
+        <v>0.9073643910721299</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.9131679478839623</v>
+        <v>0.9131679478839624</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.4185969270932782</v>
+        <v>-0.4185969270932779</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.8209210743406011</v>
+        <v>0.8209210743406012</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.9300276538380745</v>
+        <v>0.9300276538380744</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.7624873102626437</v>
+        <v>0.7624873102626444</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.8266151212697095</v>
+        <v>0.8266151212697096</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.8923871859889412</v>
+        <v>0.8923871859889413</v>
       </c>
       <c r="CF9" t="n">
         <v>0.912094055584558</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.3769646640240791</v>
+        <v>0.3769646640240787</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.9034217341932965</v>
+        <v>0.903421734193297</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.9364979228212886</v>
+        <v>0.9364979228212884</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.2262395907041435</v>
+        <v>0.2262395907041437</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.8718945424922805</v>
+        <v>0.8718945424922799</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.9213310184171466</v>
+        <v>0.9213310184171467</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.8237950096833991</v>
+        <v>0.8237950096833979</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.9402841219439841</v>
+        <v>0.9402841219439843</v>
       </c>
       <c r="CO9" t="n">
         <v>0.6396397943403278</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.5592625867859368</v>
+        <v>0.5592625867859373</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.0216692713447954</v>
+        <v>-0.02166927134479452</v>
       </c>
       <c r="CR9" t="n">
         <v>0.9010876271811232</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.932018079778001</v>
+        <v>0.9320180797780013</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.9019810782710124</v>
+        <v>0.9019810782710121</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.8848489673057042</v>
+        <v>0.8848489673057041</v>
       </c>
       <c r="CV9" t="n">
         <v>0.9034419777895891</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.8974706317898202</v>
+        <v>0.8974706317898199</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.8915350574194525</v>
+        <v>0.8915350574194523</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.8936926991084946</v>
+        <v>0.8936926991084948</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.8736723880965926</v>
+        <v>0.8736723880965928</v>
       </c>
       <c r="DA9" t="n">
         <v>0.8581282500724583</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.8412201712112379</v>
+        <v>0.841220171211237</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.9143148613610379</v>
+        <v>0.914314861361038</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.886397862827801</v>
+        <v>0.8863978628278013</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.8851243759812228</v>
+        <v>0.8851243759812022</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.8571851329499335</v>
+        <v>0.8571851329499338</v>
       </c>
       <c r="DG9" t="n">
         <v>0.881084519551645</v>
@@ -4433,37 +4433,37 @@
         <v>0.9218757972961251</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.8846104405618311</v>
+        <v>0.8846104405618312</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.8345757030894367</v>
+        <v>0.8345757030894368</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.9364898667904027</v>
+        <v>0.9364898667904029</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.8653026833712458</v>
+        <v>0.8653026833712467</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.9384460877211036</v>
+        <v>0.9384460877211034</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9247296670970165</v>
+        <v>0.9247296670970164</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.8426230073628237</v>
+        <v>0.8426230073628236</v>
       </c>
       <c r="DP9" t="n">
         <v>0.9574662276620367</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.005440060261289098</v>
+        <v>0.005440060261287544</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.2766124864963466</v>
+        <v>0.2766124864963477</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.9260368361871264</v>
+        <v>0.9260368361871265</v>
       </c>
       <c r="DT9" t="n">
         <v>0.7890919916560304</v>
@@ -4472,19 +4472,19 @@
         <v>0.8662252673209316</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.9032229645114869</v>
+        <v>0.9032229645114874</v>
       </c>
       <c r="DW9" t="n">
         <v>0.9361257484148423</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.77943728730813</v>
+        <v>0.7794372873081299</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.9251025827251825</v>
+        <v>0.9251025827251823</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.893677799895326</v>
+        <v>0.8936777998953261</v>
       </c>
       <c r="EA9" t="n">
         <v>0.9368382892905518</v>
@@ -4493,28 +4493,28 @@
         <v>0.9143481946071267</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.95317771524809</v>
+        <v>0.9531777152480901</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.2223615905732242</v>
+        <v>0.2223615905732229</v>
       </c>
       <c r="EE9" t="n">
         <v>0.9103715178587568</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.01227099828823339</v>
+        <v>0.01227099828822256</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.6250924647680358</v>
+        <v>0.6250924647680348</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.7055625289491798</v>
+        <v>0.7055625289491728</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.7665738281591238</v>
+        <v>0.7665738281591264</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.7521138677899371</v>
+        <v>0.7521138677899381</v>
       </c>
     </row>
     <row r="10">
@@ -4524,52 +4524,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9690211472822818</v>
+        <v>0.9690211472822822</v>
       </c>
       <c r="C10" t="n">
         <v>0.7207020787079508</v>
       </c>
       <c r="D10" t="n">
-        <v>0.984508499915645</v>
+        <v>0.9845084999156455</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8966285715731963</v>
+        <v>0.9720998484829029</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9536063467706611</v>
+        <v>0.9536063467706613</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9840066959867737</v>
+        <v>0.9840066959867736</v>
       </c>
       <c r="H10" t="n">
         <v>0.9438952954847128</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8987313863852311</v>
+        <v>0.8987313863852313</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9623047199253683</v>
+        <v>0.9247842362373417</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8805647166611978</v>
+        <v>0.8805647166611981</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9861687513716541</v>
+        <v>0.9861687513716537</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7183864466681165</v>
+        <v>0.7183864466681164</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7943289358700933</v>
+        <v>0.7943289358700938</v>
       </c>
       <c r="O10" t="n">
         <v>0.8215970188660751</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9663171304042424</v>
+        <v>0.9663171304042428</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7898699365210679</v>
+        <v>0.7898699365210681</v>
       </c>
       <c r="R10" t="n">
         <v>0.9784457656736647</v>
@@ -4578,148 +4578,148 @@
         <v>0.9846556669896962</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9870349734681961</v>
+        <v>0.987034973468196</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9610987769038241</v>
+        <v>0.9610987769038242</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9823178600975415</v>
+        <v>0.9823178600975414</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8698814106549002</v>
+        <v>0.8698814106548998</v>
       </c>
       <c r="X10" t="n">
         <v>0.9754458299273836</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9822411479225047</v>
+        <v>0.9822411479225046</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9475246253109</v>
+        <v>0.9475246253109002</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.986819992995718</v>
+        <v>0.9868199929957181</v>
       </c>
       <c r="AB10" t="n">
         <v>0.9873900420796979</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.9449282058299626</v>
+        <v>0.944928205829963</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.7468263346474514</v>
+        <v>0.7468263346474523</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.925116856189526</v>
+        <v>0.9251168561895272</v>
       </c>
       <c r="AF10" t="n">
         <v>0.9801227683567846</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.9085538144118597</v>
+        <v>0.9085538144118595</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.9927936880679133</v>
+        <v>0.9927936880679136</v>
       </c>
       <c r="AI10" t="n">
         <v>0.972384375837007</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.9854440995172687</v>
+        <v>0.9854440995172686</v>
       </c>
       <c r="AK10" t="n">
         <v>0.9081955759870896</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.9751736875617203</v>
+        <v>0.97517368756172</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.9510081986422565</v>
+        <v>0.9510081986422563</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.9853305693524657</v>
+        <v>0.9853305693524658</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.9251596257326562</v>
+        <v>0.9251596257326555</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.8790395310807557</v>
+        <v>0.8790395310807555</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.9787844319540719</v>
+        <v>0.9787844319540718</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.989954494693806</v>
+        <v>0.9899544946938059</v>
       </c>
       <c r="AS10" t="n">
         <v>0.9845468926812406</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.7770252057194099</v>
+        <v>0.7770252057194107</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8531752878140508</v>
+        <v>0.8531752878140522</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.9675365730495927</v>
+        <v>0.9675365730495926</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.9451512689468942</v>
+        <v>0.9451512689468938</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.9949435129950434</v>
+        <v>0.9949435129950436</v>
       </c>
       <c r="AY10" t="n">
         <v>0.9851032686856326</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.9432460433150385</v>
+        <v>0.9432460433150386</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.8909836647532998</v>
+        <v>0.8909836647533016</v>
       </c>
       <c r="BB10" t="n">
         <v>0.9593303390792659</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.956341633888305</v>
+        <v>0.9563416338883046</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.9295230632068934</v>
+        <v>0.9295230632068932</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.969706298709769</v>
+        <v>0.9697062987097691</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.9561217922286352</v>
+        <v>0.9561217922286347</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.9160154701542088</v>
+        <v>0.9160154701542086</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.9217836532820236</v>
+        <v>0.9217836532820237</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.9523442931121024</v>
+        <v>0.9523442931121023</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.03754570011026501</v>
+        <v>-0.03754570011026503</v>
       </c>
       <c r="BK10" t="n">
         <v>-0.411100362467235</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.9831411047682812</v>
+        <v>0.9831411047682814</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.8339378337924942</v>
+        <v>0.8339378337924941</v>
       </c>
       <c r="BN10" t="n">
         <v>0.9700386887988586</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.4595806438346322</v>
+        <v>0.4595806438346316</v>
       </c>
       <c r="BP10" t="n">
         <v>0.9761379189148174</v>
@@ -4728,13 +4728,13 @@
         <v>0.9734518955432783</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0.498173776666834</v>
+        <v>-0.4981737766668344</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.8822851938997057</v>
+        <v>0.8822851938997056</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.9827173293845002</v>
+        <v>0.9827173293845</v>
       </c>
       <c r="BU10" t="n">
         <v>0.9660709487884644</v>
@@ -4743,22 +4743,22 @@
         <v>0.9609836286247593</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.7076751104842963</v>
+        <v>0.7076751104842973</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.9824446051468709</v>
+        <v>0.9824446051468712</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.9622913685759653</v>
+        <v>0.9622913685759658</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.4164470837865052</v>
+        <v>-0.416447083786505</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.9254456527166033</v>
+        <v>0.9254456527166032</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.9744685735816272</v>
+        <v>0.974468573581627</v>
       </c>
       <c r="CC10" t="n">
         <v>0.8704459880542659</v>
@@ -4767,142 +4767,142 @@
         <v>0.9108761831101453</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.955401936024604</v>
+        <v>0.9554019360246039</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.9697356245040614</v>
+        <v>0.9697356245040615</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.4647924172165985</v>
+        <v>0.4647924172165983</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.9804961725096351</v>
+        <v>0.9804961725096353</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.9570042981453467</v>
+        <v>0.9570042981453465</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.3833354901378997</v>
+        <v>0.3833354901378999</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.9377045133175533</v>
+        <v>0.9377045133175524</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.9610643828596491</v>
+        <v>0.9610643828596492</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.9098109651718996</v>
+        <v>0.9098109651718991</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.978281091984826</v>
+        <v>0.9782810919848259</v>
       </c>
       <c r="CO10" t="n">
         <v>0.6600622889421646</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.7038713621052998</v>
+        <v>0.7038713621052999</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.1823677693922293</v>
+        <v>0.1823677693922303</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.9670834344726834</v>
+        <v>0.9670834344726835</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.9759775104286692</v>
+        <v>0.9759775104286693</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.9709169804002341</v>
+        <v>0.9709169804002342</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.9562764792554084</v>
+        <v>0.9562764792554087</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.9842431446332413</v>
+        <v>0.9842431446332414</v>
       </c>
       <c r="CW10" t="n">
         <v>0.9686365642986384</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.9622204082743834</v>
+        <v>0.9622204082743835</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.9622883510367566</v>
+        <v>0.9622883510367564</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.9487746269969053</v>
+        <v>0.9487746269969055</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.963851471259773</v>
+        <v>0.9638514712597729</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.9331693944969244</v>
+        <v>0.9331693944969239</v>
       </c>
       <c r="DC10" t="n">
         <v>0.9127105663910726</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.9764132889806062</v>
+        <v>0.9764132889806065</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.943423239739365</v>
+        <v>0.9434232397393644</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.9350035403882023</v>
+        <v>0.9350035403882024</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.9790369344370483</v>
+        <v>0.9790369344370485</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.9631042697410834</v>
+        <v>0.9631042697410833</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.9594626602507538</v>
+        <v>0.959462660250754</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.9187203911354632</v>
+        <v>0.9187203911354636</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.9901151017199187</v>
+        <v>0.9901151017199188</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.9587340550668463</v>
+        <v>0.9587340550668468</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.9721556801769923</v>
+        <v>0.9721556801769922</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.9737932586376942</v>
+        <v>0.9737932586376944</v>
       </c>
       <c r="DO10" t="n">
         <v>0.9111992904948265</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.9864346368187299</v>
+        <v>0.9864346368187298</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.06038790802616575</v>
+        <v>0.06038790802616427</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.3993331929136555</v>
+        <v>0.3993331929136565</v>
       </c>
       <c r="DS10" t="n">
         <v>0.9803144302881722</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.9186933120756923</v>
+        <v>0.9186933120756922</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.9224961516063613</v>
+        <v>0.9224961516063612</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.8974628260787437</v>
+        <v>0.8974628260787449</v>
       </c>
       <c r="DW10" t="n">
         <v>0.9791683730338434</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.8963919353313599</v>
+        <v>0.89639193533136</v>
       </c>
       <c r="DY10" t="n">
         <v>0.9829712447538669</v>
@@ -4914,31 +4914,31 @@
         <v>0.9825762009914299</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.9822815221901884</v>
+        <v>0.9822815221901883</v>
       </c>
       <c r="EC10" t="n">
         <v>0.9830131873051586</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.145346415245692</v>
+        <v>0.1453464152456914</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.974931620832693</v>
+        <v>0.9749316208326931</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.01963188906858358</v>
+        <v>-0.01963188906859493</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.6731531874709348</v>
+        <v>0.6731531874709341</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.7909603099272733</v>
+        <v>0.7909603099272697</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.8377901822918764</v>
+        <v>0.8377901822918778</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.8782294886540015</v>
+        <v>0.8782294886540023</v>
       </c>
     </row>
   </sheetData>
